--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T14:07:32+00:00</t>
+    <t>2026-09-17T10:04:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T10:04:49+00:00</t>
+    <t>2026-09-17T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T10:08:33+00:00</t>
+    <t>2026-09-17T12:36:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:36:17+00:00</t>
+    <t>2026-10-13T07:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
